--- a/Data/ModelResponse/3/evaluation/3_evaluation_summary.xlsx
+++ b/Data/ModelResponse/3/evaluation/3_evaluation_summary.xlsx
@@ -531,43 +531,43 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>15551</v>
+        <v>15489</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8099479166666667</v>
+        <v>0.80671875</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8099479166666667</v>
+        <v>0.80671875</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8374671391016116</v>
+        <v>0.8366947101532788</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7669039145907474</v>
+        <v>0.7598911450701277</v>
       </c>
       <c r="K2" t="n">
-        <v>0.800633775883735</v>
+        <v>0.7964456146124732</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7869103435077983</v>
+        <v>0.782001330419082</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8525813808832676</v>
+        <v>0.8530997304582211</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8184306115340598</v>
+        <v>0.8160047597798602</v>
       </c>
       <c r="O2" t="n">
-        <v>7327</v>
+        <v>7260</v>
       </c>
       <c r="P2" t="n">
-        <v>2227</v>
+        <v>2294</v>
       </c>
       <c r="Q2" t="n">
-        <v>1422</v>
+        <v>1417</v>
       </c>
       <c r="R2" t="n">
-        <v>8224</v>
+        <v>8229</v>
       </c>
     </row>
   </sheetData>
@@ -695,43 +695,43 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>700</v>
+        <v>677</v>
       </c>
       <c r="G2" t="n">
-        <v>0.875</v>
+        <v>0.8462499999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.875</v>
+        <v>0.8462499999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8953168044077136</v>
+        <v>0.8687150837988827</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8397932816537468</v>
+        <v>0.8036175710594315</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8348993288590605</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8581235697940504</v>
+        <v>0.8280542986425339</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9079903147699758</v>
+        <v>0.8861985472154964</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.8561403508771929</v>
       </c>
       <c r="O2" t="n">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="P2" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="Q2" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="R2" t="n">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3">
@@ -753,43 +753,43 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8875</v>
+        <v>0.88125</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8875</v>
+        <v>0.88125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9153439153439153</v>
+        <v>0.9076517150395779</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8564356435643564</v>
+        <v>0.8514851485148515</v>
       </c>
       <c r="K3" t="n">
-        <v>0.884910485933504</v>
+        <v>0.8786717752234993</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8625592417061612</v>
+        <v>0.8574821852731591</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9191919191919192</v>
+        <v>0.9116161616161617</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8899755501222494</v>
+        <v>0.8837209302325582</v>
       </c>
       <c r="O3" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="P3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q3" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="R3" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4">
@@ -811,43 +811,43 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1103</v>
+        <v>1120</v>
       </c>
       <c r="G4" t="n">
-        <v>0.689375</v>
+        <v>0.7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.689375</v>
+        <v>0.7</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7842105263157895</v>
+        <v>0.7996485061511424</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5444579780755177</v>
+        <v>0.5542021924482339</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6427030913012222</v>
+        <v>0.6546762589928058</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6368932038834951</v>
+        <v>0.6450048496605237</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.8536585365853658</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7252625760088447</v>
+        <v>0.734806629834254</v>
       </c>
       <c r="O4" t="n">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="P4" t="n">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="Q4" t="n">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="R4" t="n">
-        <v>656</v>
+        <v>665</v>
       </c>
     </row>
     <row r="5">
@@ -869,37 +869,37 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1242</v>
+        <v>1207</v>
       </c>
       <c r="G5" t="n">
-        <v>0.77625</v>
+        <v>0.754375</v>
       </c>
       <c r="H5" t="n">
-        <v>0.77625</v>
+        <v>0.754375</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7632508833922261</v>
+        <v>0.7530712530712531</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8049689440993789</v>
+        <v>0.7614906832298136</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7835550181378477</v>
+        <v>0.7572575663990117</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7909454061251664</v>
+        <v>0.7557251908396947</v>
       </c>
       <c r="M5" t="n">
         <v>0.7471698113207547</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7684346701164294</v>
+        <v>0.7514231499051234</v>
       </c>
       <c r="O5" t="n">
-        <v>648</v>
+        <v>613</v>
       </c>
       <c r="P5" t="n">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="Q5" t="n">
         <v>201</v>
@@ -927,43 +927,43 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1337</v>
+        <v>1345</v>
       </c>
       <c r="G6" t="n">
-        <v>0.835625</v>
+        <v>0.840625</v>
       </c>
       <c r="H6" t="n">
-        <v>0.835625</v>
+        <v>0.840625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8244186046511628</v>
+        <v>0.8337264150943396</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8635809987819733</v>
+        <v>0.8611449451887941</v>
       </c>
       <c r="K6" t="n">
-        <v>0.843545508625818</v>
+        <v>0.8472139005392452</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8486486486486486</v>
+        <v>0.848404255319149</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8061617458279846</v>
+        <v>0.8189987163029525</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8268597761685319</v>
+        <v>0.8334421946440236</v>
       </c>
       <c r="O6" t="n">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="P6" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q6" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="R6" t="n">
-        <v>628</v>
+        <v>638</v>
       </c>
     </row>
     <row r="7">
@@ -985,43 +985,43 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1468</v>
+        <v>1476</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9175</v>
+        <v>0.9225</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9175</v>
+        <v>0.9225</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9305949008498584</v>
+        <v>0.9338028169014084</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8878378378378379</v>
+        <v>0.8959459459459459</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9087136929460581</v>
+        <v>0.9144827586206896</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9071588366890381</v>
+        <v>0.9134831460674158</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9430232558139535</v>
+        <v>0.9453488372093023</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9247434435575826</v>
+        <v>0.929142857142857</v>
       </c>
       <c r="O7" t="n">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="P7" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="Q7" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="R7" t="n">
-        <v>811</v>
+        <v>813</v>
       </c>
     </row>
     <row r="8">
@@ -1043,43 +1043,43 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1476</v>
+        <v>1465</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9225</v>
+        <v>0.915625</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9225</v>
+        <v>0.915625</v>
       </c>
       <c r="I8" t="n">
-        <v>0.915057915057915</v>
+        <v>0.9149214659685864</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9245773732119635</v>
+        <v>0.9089726918075423</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9197930142302716</v>
+        <v>0.9119373776908022</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9295261239368166</v>
+        <v>0.916267942583732</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9205776173285198</v>
+        <v>0.9217809867629362</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9250302297460701</v>
+        <v>0.9190161967606478</v>
       </c>
       <c r="O8" t="n">
-        <v>711</v>
+        <v>699</v>
       </c>
       <c r="P8" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="Q8" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R8" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="9">
@@ -1101,37 +1101,37 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1210</v>
+        <v>1189</v>
       </c>
       <c r="G9" t="n">
-        <v>0.75625</v>
+        <v>0.743125</v>
       </c>
       <c r="H9" t="n">
-        <v>0.75625</v>
+        <v>0.743125</v>
       </c>
       <c r="I9" t="n">
-        <v>0.78125</v>
+        <v>0.7751004016064257</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7299270072992701</v>
+        <v>0.7043795620437956</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7547169811320755</v>
+        <v>0.7380497131931165</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7331730769230769</v>
+        <v>0.7151230949589683</v>
       </c>
       <c r="M9" t="n">
         <v>0.7840616966580977</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7577639751552795</v>
+        <v>0.7480073574494175</v>
       </c>
       <c r="O9" t="n">
-        <v>600</v>
+        <v>579</v>
       </c>
       <c r="P9" t="n">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="Q9" t="n">
         <v>168</v>
@@ -1159,43 +1159,43 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1389</v>
+        <v>1381</v>
       </c>
       <c r="G10" t="n">
-        <v>0.868125</v>
+        <v>0.863125</v>
       </c>
       <c r="H10" t="n">
-        <v>0.868125</v>
+        <v>0.863125</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8517200474495848</v>
+        <v>0.8429073856975381</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8930348258706468</v>
+        <v>0.8942786069651741</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8718882817243473</v>
+        <v>0.867833433916717</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8863936591809776</v>
+        <v>0.8862115127175368</v>
       </c>
       <c r="M10" t="n">
-        <v>0.842964824120603</v>
+        <v>0.8316582914572864</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8641339343206698</v>
+        <v>0.8580686973428386</v>
       </c>
       <c r="O10" t="n">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="P10" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q10" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="R10" t="n">
-        <v>671</v>
+        <v>662</v>
       </c>
     </row>
     <row r="11">
@@ -1217,43 +1217,43 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="G11" t="n">
-        <v>0.719375</v>
+        <v>0.7162500000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.719375</v>
+        <v>0.7162500000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8050420168067227</v>
+        <v>0.8013468013468014</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5899014778325123</v>
+        <v>0.5862068965517241</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6808813077469795</v>
+        <v>0.6770981507823612</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6686567164179105</v>
+        <v>0.6660039761431411</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8527918781725888</v>
+        <v>0.850253807106599</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7495817066369214</v>
+        <v>0.7469342251950948</v>
       </c>
       <c r="O11" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="P11" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q11" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="R11" t="n">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="12">
@@ -1275,43 +1275,43 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1413</v>
+        <v>1422</v>
       </c>
       <c r="G12" t="n">
-        <v>0.883125</v>
+        <v>0.88875</v>
       </c>
       <c r="H12" t="n">
-        <v>0.883125</v>
+        <v>0.88875</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9286733238231099</v>
+        <v>0.9472140762463344</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8261421319796954</v>
+        <v>0.8197969543147208</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8744123572867697</v>
+        <v>0.8789115646258503</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8476084538375973</v>
+        <v>0.8453159041394336</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9384236453201971</v>
+        <v>0.9556650246305419</v>
       </c>
       <c r="N12" t="n">
-        <v>0.890707188778492</v>
+        <v>0.8971098265895954</v>
       </c>
       <c r="O12" t="n">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="P12" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="Q12" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="R12" t="n">
-        <v>762</v>
+        <v>776</v>
       </c>
     </row>
     <row r="13">
@@ -1333,43 +1333,43 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="G13" t="n">
-        <v>0.718125</v>
+        <v>0.720625</v>
       </c>
       <c r="H13" t="n">
-        <v>0.718125</v>
+        <v>0.720625</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7527932960893855</v>
+        <v>0.7506849315068493</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6629766297662977</v>
+        <v>0.6740467404674046</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7050359712230215</v>
+        <v>0.7103046014257939</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6900452488687783</v>
+        <v>0.6954022988505747</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7750952986022872</v>
+        <v>0.7687420584498094</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7301017354877318</v>
+        <v>0.7302353651176825</v>
       </c>
       <c r="O13" t="n">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="P13" t="n">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="Q13" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="R13" t="n">
-        <v>610</v>
+        <v>605</v>
       </c>
     </row>
     <row r="14">
@@ -1400,34 +1400,34 @@
         <v>0.751875</v>
       </c>
       <c r="I14" t="n">
-        <v>0.797752808988764</v>
+        <v>0.794912559618442</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6471354166666666</v>
+        <v>0.6510416666666666</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7145938173975558</v>
+        <v>0.7158196134574086</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7226202661207779</v>
+        <v>0.7239958805355304</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8485576923076923</v>
+        <v>0.8449519230769231</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7805417357656164</v>
+        <v>0.7798114254021077</v>
       </c>
       <c r="O14" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="P14" t="n">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Q14" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="R14" t="n">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
   </sheetData>
@@ -1555,43 +1555,43 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7472527472527473</v>
+        <v>0.8</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7640449438202247</v>
+        <v>0.7191011235955056</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7555555555555554</v>
+        <v>0.7573964497041421</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7920792079207921</v>
+        <v>0.7767857142857143</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7766990291262136</v>
+        <v>0.8446601941747572</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7843137254901961</v>
+        <v>0.8093023255813954</v>
       </c>
       <c r="O2" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="P2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="R2" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
@@ -1613,43 +1613,43 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8170731707317073</v>
+        <v>0.8117647058823529</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7204301075268817</v>
+        <v>0.7419354838709677</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7657142857142857</v>
+        <v>0.7752808988764045</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7636363636363637</v>
+        <v>0.7757009345794392</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.8383838383838383</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8038277511961722</v>
+        <v>0.8058252427184466</v>
       </c>
       <c r="O3" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4">
@@ -1671,37 +1671,37 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8072916666666666</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8072916666666666</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9195402298850575</v>
+        <v>0.9213483146067416</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7454545454545455</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8121827411167513</v>
+        <v>0.8241206030150754</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7281553398058253</v>
       </c>
       <c r="M4" t="n">
         <v>0.9146341463414634</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8021390374331552</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="O4" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="n">
         <v>7</v>
@@ -1729,43 +1729,43 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7978723404255319</v>
+        <v>0.8369565217391305</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7731958762886598</v>
+        <v>0.7938144329896907</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7853403141361256</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7755102040816326</v>
+        <v>0.8</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7875647668393783</v>
+        <v>0.8205128205128205</v>
       </c>
       <c r="O5" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
@@ -1787,43 +1787,43 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G6" t="n">
-        <v>0.84375</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="H6" t="n">
-        <v>0.84375</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8762886597938144</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8252427184466019</v>
+        <v>0.7572815533980582</v>
       </c>
       <c r="K6" t="n">
-        <v>0.85</v>
+        <v>0.8210526315789473</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8105263157894737</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8651685393258427</v>
+        <v>0.898876404494382</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8369565217391305</v>
+        <v>0.8247422680412371</v>
       </c>
       <c r="O6" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="P6" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="R6" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -1845,31 +1845,31 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8604651162790697</v>
+        <v>0.8314606741573034</v>
       </c>
       <c r="J7" t="n">
         <v>0.7872340425531915</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8222222222222222</v>
+        <v>0.808743169398907</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8113207547169812</v>
+        <v>0.8058252427184466</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.8469387755102041</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8431372549019608</v>
+        <v>0.8258706467661691</v>
       </c>
       <c r="O7" t="n">
         <v>74</v>
@@ -1878,10 +1878,10 @@
         <v>20</v>
       </c>
       <c r="Q7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="R7" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8">
@@ -1903,43 +1903,43 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="G8" t="n">
-        <v>0.828125</v>
+        <v>0.859375</v>
       </c>
       <c r="H8" t="n">
-        <v>0.828125</v>
+        <v>0.859375</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8641975308641975</v>
+        <v>0.9012345679012346</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7608695652173914</v>
+        <v>0.7934782608695652</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8092485549132948</v>
+        <v>0.8439306358381502</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8018018018018018</v>
+        <v>0.8288288288288288</v>
       </c>
       <c r="M8" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8436018957345972</v>
+        <v>0.8720379146919431</v>
       </c>
       <c r="O8" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R8" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9">
@@ -1961,37 +1961,37 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9397590361445783</v>
+        <v>0.9390243902439024</v>
       </c>
       <c r="J9" t="n">
-        <v>0.75</v>
+        <v>0.7403846153846154</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8342245989304812</v>
+        <v>0.8279569892473119</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7614678899082569</v>
+        <v>0.7545454545454545</v>
       </c>
       <c r="M9" t="n">
         <v>0.9431818181818182</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8426395939086295</v>
+        <v>0.8383838383838385</v>
       </c>
       <c r="O9" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q9" t="n">
         <v>5</v>
@@ -2019,31 +2019,31 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7840909090909091</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="J10" t="n">
         <v>0.6509433962264151</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7113402061855669</v>
+        <v>0.7040816326530612</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6442307692307693</v>
+        <v>0.6372549019607843</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7790697674418605</v>
+        <v>0.7558139534883721</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7052631578947369</v>
+        <v>0.6914893617021277</v>
       </c>
       <c r="O10" t="n">
         <v>69</v>
@@ -2052,10 +2052,10 @@
         <v>37</v>
       </c>
       <c r="Q10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">
@@ -2077,31 +2077,31 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8351648351648352</v>
+        <v>0.7676767676767676</v>
       </c>
       <c r="J11" t="n">
         <v>0.7916666666666666</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8128342245989305</v>
+        <v>0.7794871794871795</v>
       </c>
       <c r="L11" t="n">
-        <v>0.801980198019802</v>
+        <v>0.7849462365591398</v>
       </c>
       <c r="M11" t="n">
-        <v>0.84375</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8223350253807107</v>
+        <v>0.7724867724867724</v>
       </c>
       <c r="O11" t="n">
         <v>76</v>
@@ -2110,10 +2110,10 @@
         <v>20</v>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="R11" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12">
@@ -2144,34 +2144,34 @@
         <v>0.8072916666666666</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8470588235294118</v>
+        <v>0.8641975308641975</v>
       </c>
       <c r="J12" t="n">
-        <v>0.75</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7955801104972374</v>
+        <v>0.7909604519774011</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7757009345794392</v>
+        <v>0.7657657657657657</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8645833333333334</v>
+        <v>0.8854166666666666</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8177339901477833</v>
+        <v>0.8212560386473429</v>
       </c>
       <c r="O12" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13">
@@ -2193,43 +2193,43 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8125</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8125</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8767123287671232</v>
       </c>
       <c r="J13" t="n">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.7573964497041421</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7310924369747899</v>
       </c>
       <c r="M13" t="n">
-        <v>0.875</v>
+        <v>0.90625</v>
       </c>
       <c r="N13" t="n">
-        <v>0.823529411764706</v>
+        <v>0.8093023255813953</v>
       </c>
       <c r="O13" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="P13" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="R13" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14">
@@ -2251,43 +2251,43 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7552083333333334</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7552083333333334</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8690476190476191</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6697247706422018</v>
+        <v>0.7155963302752294</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7564766839378239</v>
+        <v>0.7839195979899497</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.696078431372549</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8674698795180723</v>
+        <v>0.8554216867469879</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7539267015706806</v>
+        <v>0.7675675675675676</v>
       </c>
       <c r="O14" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="P14" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R14" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
@@ -2309,31 +2309,31 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G15" t="n">
-        <v>0.734375</v>
+        <v>0.7239583333333334</v>
       </c>
       <c r="H15" t="n">
-        <v>0.734375</v>
+        <v>0.7239583333333334</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7171717171717171</v>
+        <v>0.7029702970297029</v>
       </c>
       <c r="J15" t="n">
         <v>0.7553191489361702</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7357512953367876</v>
+        <v>0.7282051282051281</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7526881720430108</v>
+        <v>0.7472527472527473</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7329842931937173</v>
+        <v>0.7195767195767196</v>
       </c>
       <c r="O15" t="n">
         <v>71</v>
@@ -2342,10 +2342,10 @@
         <v>23</v>
       </c>
       <c r="Q15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R15" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16">
@@ -2367,37 +2367,37 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8089887640449438</v>
+        <v>0.8045977011494253</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8044692737430168</v>
+        <v>0.7909604519774011</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8252427184466019</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="M16" t="n">
         <v>0.8333333333333334</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8292682926829268</v>
+        <v>0.8212560386473431</v>
       </c>
       <c r="O16" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q16" t="n">
         <v>17</v>
@@ -2425,43 +2425,43 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.8125</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.8125</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8260869565217391</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7407407407407407</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7947019867549669</v>
+        <v>0.76</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8278688524590164</v>
+        <v>0.8048780487804879</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9099099099099099</v>
+        <v>0.8918918918918919</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8669527896995709</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="P17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R17" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18">
@@ -2483,43 +2483,43 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G18" t="n">
-        <v>0.734375</v>
+        <v>0.703125</v>
       </c>
       <c r="H18" t="n">
-        <v>0.734375</v>
+        <v>0.703125</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8068181818181818</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6761904761904762</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7357512953367875</v>
+        <v>0.7076923076923077</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6730769230769231</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8045977011494253</v>
+        <v>0.7586206896551724</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7329842931937174</v>
+        <v>0.6984126984126984</v>
       </c>
       <c r="O18" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q18" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="R18" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
@@ -2541,43 +2541,43 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.78125</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.78125</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8591549295774648</v>
+        <v>0.8873239436619719</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6288659793814433</v>
+        <v>0.6494845360824743</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7261904761904762</v>
+        <v>0.7500000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7024793388429752</v>
+        <v>0.71900826446281</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.9157894736842105</v>
       </c>
       <c r="N19" t="n">
-        <v>0.787037037037037</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="O19" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P19" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R19" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20">
@@ -2599,43 +2599,43 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9010416666666666</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9010416666666666</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8809523809523809</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8915662650602409</v>
+        <v>0.9036144578313253</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8862275449101796</v>
+        <v>0.8823529411764707</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9238095238095239</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9082568807339449</v>
+        <v>0.8899082568807339</v>
       </c>
       <c r="N20" t="n">
-        <v>0.912442396313364</v>
+        <v>0.9065420560747663</v>
       </c>
       <c r="O20" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R20" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21">
@@ -2657,43 +2657,43 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G21" t="n">
-        <v>0.78125</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="H21" t="n">
-        <v>0.78125</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8701298701298701</v>
+        <v>0.8860759493670886</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6767676767676768</v>
+        <v>0.7070707070707071</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7613636363636364</v>
+        <v>0.7865168539325842</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7217391304347827</v>
+        <v>0.7433628318584071</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8924731182795699</v>
+        <v>0.9032258064516129</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7980769230769232</v>
+        <v>0.8155339805825244</v>
       </c>
       <c r="O21" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P21" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22">
@@ -2715,43 +2715,43 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G22" t="n">
-        <v>0.796875</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="H22" t="n">
-        <v>0.796875</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7407407407407407</v>
+        <v>0.7530864197530864</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7547169811320754</v>
+        <v>0.782051282051282</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.8290598290598291</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8378378378378378</v>
+        <v>0.8738738738738738</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8266666666666665</v>
+        <v>0.8508771929824561</v>
       </c>
       <c r="O22" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q22" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="R22" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23">
@@ -2782,34 +2782,34 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="I23" t="n">
-        <v>0.775</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7380952380952381</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7560975609756099</v>
+        <v>0.7500000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8035714285714286</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8214285714285715</v>
       </c>
       <c r="O23" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R23" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24">
@@ -2889,43 +2889,43 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G25" t="n">
-        <v>0.796875</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="H25" t="n">
-        <v>0.796875</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8409090909090909</v>
+        <v>0.7888888888888889</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7474747474747475</v>
+        <v>0.7171717171717171</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7914438502673797</v>
+        <v>0.7513227513227514</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7596153846153846</v>
+        <v>0.7254901960784313</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8494623655913979</v>
+        <v>0.7956989247311828</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8020304568527918</v>
+        <v>0.7589743589743591</v>
       </c>
       <c r="O25" t="n">
+        <v>71</v>
+      </c>
+      <c r="P25" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>19</v>
+      </c>
+      <c r="R25" t="n">
         <v>74</v>
-      </c>
-      <c r="P25" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>14</v>
-      </c>
-      <c r="R25" t="n">
-        <v>79</v>
       </c>
     </row>
     <row r="26">
@@ -2947,43 +2947,43 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G26" t="n">
-        <v>0.828125</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H26" t="n">
-        <v>0.828125</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7934782608695652</v>
+        <v>0.8160919540229885</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8390804597701149</v>
+        <v>0.8160919540229885</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8156424581005586</v>
+        <v>0.8160919540229885</v>
       </c>
       <c r="L26" t="n">
-        <v>0.86</v>
+        <v>0.8476190476190476</v>
       </c>
       <c r="M26" t="n">
-        <v>0.819047619047619</v>
+        <v>0.8476190476190476</v>
       </c>
       <c r="N26" t="n">
-        <v>0.8390243902439023</v>
+        <v>0.8476190476190476</v>
       </c>
       <c r="O26" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q26" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="R26" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27">
@@ -3014,34 +3014,34 @@
         <v>0.8385416666666666</v>
       </c>
       <c r="I27" t="n">
-        <v>0.85</v>
+        <v>0.8723404255319149</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8415841584158416</v>
+        <v>0.8118811881188119</v>
       </c>
       <c r="K27" t="n">
-        <v>0.845771144278607</v>
+        <v>0.841025641025641</v>
       </c>
       <c r="L27" t="n">
-        <v>0.8260869565217391</v>
+        <v>0.8061224489795918</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8351648351648352</v>
+        <v>0.8681318681318682</v>
       </c>
       <c r="N27" t="n">
-        <v>0.8306010928961749</v>
+        <v>0.8359788359788359</v>
       </c>
       <c r="O27" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P27" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q27" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="R27" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28">
@@ -3121,43 +3121,43 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.8125</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.8125</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8170731707317073</v>
+        <v>0.8068181818181818</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7888888888888889</v>
       </c>
       <c r="K29" t="n">
-        <v>0.7790697674418605</v>
+        <v>0.797752808988764</v>
       </c>
       <c r="L29" t="n">
-        <v>0.7909090909090909</v>
+        <v>0.8173076923076923</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8529411764705882</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N29" t="n">
-        <v>0.820754716981132</v>
+        <v>0.825242718446602</v>
       </c>
       <c r="O29" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="P29" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R29" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30">
@@ -3179,43 +3179,43 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.78125</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.78125</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8314606741573034</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7474747474747475</v>
+        <v>0.7676767676767676</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7872340425531915</v>
+        <v>0.7835051546391752</v>
       </c>
       <c r="L30" t="n">
-        <v>0.7572815533980582</v>
+        <v>0.7628865979381443</v>
       </c>
       <c r="M30" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.7956989247311828</v>
       </c>
       <c r="N30" t="n">
-        <v>0.7959183673469389</v>
+        <v>0.7789473684210526</v>
       </c>
       <c r="O30" t="n">
+        <v>76</v>
+      </c>
+      <c r="P30" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>19</v>
+      </c>
+      <c r="R30" t="n">
         <v>74</v>
-      </c>
-      <c r="P30" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>15</v>
-      </c>
-      <c r="R30" t="n">
-        <v>78</v>
       </c>
     </row>
     <row r="31">
@@ -3237,31 +3237,31 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8072916666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8072916666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8395061728395061</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="J31" t="n">
         <v>0.7391304347826086</v>
       </c>
       <c r="K31" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="L31" t="n">
-        <v>0.7837837837837838</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="M31" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="N31" t="n">
-        <v>0.8246445497630331</v>
+        <v>0.851851851851852</v>
       </c>
       <c r="O31" t="n">
         <v>68</v>
@@ -3270,10 +3270,10 @@
         <v>24</v>
       </c>
       <c r="Q31" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R31" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32">
@@ -3295,31 +3295,31 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.796875</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.796875</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8311688311688312</v>
+        <v>0.8205128205128205</v>
       </c>
       <c r="J32" t="n">
         <v>0.7191011235955056</v>
       </c>
       <c r="K32" t="n">
-        <v>0.7710843373493976</v>
+        <v>0.7664670658682635</v>
       </c>
       <c r="L32" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.7807017543859649</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8737864077669902</v>
+        <v>0.8640776699029126</v>
       </c>
       <c r="N32" t="n">
-        <v>0.8256880733944955</v>
+        <v>0.8202764976958525</v>
       </c>
       <c r="O32" t="n">
         <v>64</v>
@@ -3328,10 +3328,10 @@
         <v>25</v>
       </c>
       <c r="Q32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R32" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33">
@@ -3353,37 +3353,37 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.84375</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.84375</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8444444444444444</v>
+        <v>0.8478260869565217</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8085106382978723</v>
+        <v>0.8297872340425532</v>
       </c>
       <c r="K33" t="n">
-        <v>0.8260869565217391</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="L33" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.84</v>
       </c>
       <c r="M33" t="n">
         <v>0.8571428571428571</v>
       </c>
       <c r="N33" t="n">
-        <v>0.84</v>
+        <v>0.8484848484848485</v>
       </c>
       <c r="O33" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P33" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q33" t="n">
         <v>14</v>
@@ -3411,37 +3411,37 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8072916666666666</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8072916666666666</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8414634146341463</v>
+        <v>0.8395061728395061</v>
       </c>
       <c r="J34" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.7311827956989247</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7885714285714285</v>
+        <v>0.7816091954022988</v>
       </c>
       <c r="L34" t="n">
-        <v>0.7818181818181819</v>
+        <v>0.7747747747747747</v>
       </c>
       <c r="M34" t="n">
         <v>0.8686868686868687</v>
       </c>
       <c r="N34" t="n">
-        <v>0.8229665071770336</v>
+        <v>0.8190476190476191</v>
       </c>
       <c r="O34" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P34" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q34" t="n">
         <v>13</v>
@@ -3469,43 +3469,43 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G35" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="I35" t="n">
         <v>0.7916666666666666</v>
       </c>
-      <c r="H35" t="n">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.7708333333333334</v>
-      </c>
       <c r="J35" t="n">
-        <v>0.8043478260869565</v>
+        <v>0.8260869565217391</v>
       </c>
       <c r="K35" t="n">
-        <v>0.7872340425531915</v>
+        <v>0.8085106382978724</v>
       </c>
       <c r="L35" t="n">
-        <v>0.8125</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="M35" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="N35" t="n">
-        <v>0.7959183673469388</v>
+        <v>0.816326530612245</v>
       </c>
       <c r="O35" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P35" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q35" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R35" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36">
@@ -3527,37 +3527,37 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G36" t="n">
-        <v>0.8072916666666666</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8072916666666666</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.8028169014084507</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7261904761904762</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="K36" t="n">
-        <v>0.7672955974842767</v>
+        <v>0.735483870967742</v>
       </c>
       <c r="L36" t="n">
-        <v>0.8034188034188035</v>
+        <v>0.7768595041322314</v>
       </c>
       <c r="M36" t="n">
         <v>0.8703703703703703</v>
       </c>
       <c r="N36" t="n">
-        <v>0.8355555555555555</v>
+        <v>0.8209606986899564</v>
       </c>
       <c r="O36" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="P36" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q36" t="n">
         <v>14</v>
@@ -3585,43 +3585,43 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="G37" t="n">
-        <v>0.7239583333333334</v>
+        <v>0.765625</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7239583333333334</v>
+        <v>0.765625</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7701149425287356</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J37" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="K37" t="n">
-        <v>0.716577540106952</v>
+        <v>0.7567567567567567</v>
       </c>
       <c r="L37" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.719626168224299</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.8369565217391305</v>
       </c>
       <c r="N37" t="n">
-        <v>0.7309644670050761</v>
+        <v>0.7738693467336683</v>
       </c>
       <c r="O37" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P37" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Q37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R37" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38">
@@ -3643,43 +3643,43 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8315789473684211</v>
+        <v>0.8125</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8061224489795918</v>
+        <v>0.7959183673469388</v>
       </c>
       <c r="K38" t="n">
-        <v>0.8186528497409326</v>
+        <v>0.8041237113402061</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8041237113402062</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8297872340425532</v>
+        <v>0.8085106382978723</v>
       </c>
       <c r="N38" t="n">
-        <v>0.8167539267015708</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="O38" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P38" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q38" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R38" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39">
@@ -3701,43 +3701,43 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="I39" t="n">
-        <v>0.775</v>
+        <v>0.7325581395348837</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7380952380952381</v>
+        <v>0.75</v>
       </c>
       <c r="K39" t="n">
-        <v>0.7560975609756099</v>
+        <v>0.7411764705882353</v>
       </c>
       <c r="L39" t="n">
-        <v>0.8035714285714286</v>
+        <v>0.8018867924528302</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7870370370370371</v>
       </c>
       <c r="N39" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.794392523364486</v>
       </c>
       <c r="O39" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q39" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R39" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40">
@@ -3759,31 +3759,31 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7760416666666666</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7760416666666666</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7835051546391752</v>
+        <v>0.8260869565217391</v>
       </c>
       <c r="J40" t="n">
         <v>0.7755102040816326</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7794871794871796</v>
+        <v>0.8</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7684210526315789</v>
+        <v>0.78</v>
       </c>
       <c r="M40" t="n">
-        <v>0.776595744680851</v>
+        <v>0.8297872340425532</v>
       </c>
       <c r="N40" t="n">
-        <v>0.7724867724867724</v>
+        <v>0.8041237113402062</v>
       </c>
       <c r="O40" t="n">
         <v>76</v>
@@ -3792,10 +3792,10 @@
         <v>22</v>
       </c>
       <c r="Q40" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="R40" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41">
@@ -3817,37 +3817,37 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G41" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8850574712643678</v>
       </c>
       <c r="J41" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7549019607843137</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="M41" t="n">
         <v>0.8850574712643678</v>
       </c>
       <c r="N41" t="n">
-        <v>0.8148148148148149</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="O41" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P41" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q41" t="n">
         <v>10</v>
@@ -3875,43 +3875,43 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G42" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.7848101265822784</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6629213483146067</v>
+        <v>0.6966292134831461</v>
       </c>
       <c r="K42" t="n">
-        <v>0.7195121951219511</v>
+        <v>0.738095238095238</v>
       </c>
       <c r="L42" t="n">
-        <v>0.7435897435897436</v>
+        <v>0.7610619469026548</v>
       </c>
       <c r="M42" t="n">
-        <v>0.8446601941747572</v>
+        <v>0.8349514563106796</v>
       </c>
       <c r="N42" t="n">
-        <v>0.7909090909090909</v>
+        <v>0.7962962962962963</v>
       </c>
       <c r="O42" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="P42" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R42" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43">
@@ -3933,37 +3933,37 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G43" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.765625</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.765625</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8611111111111112</v>
+        <v>0.863013698630137</v>
       </c>
       <c r="J43" t="n">
-        <v>0.6326530612244898</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="K43" t="n">
-        <v>0.7294117647058823</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="L43" t="n">
-        <v>0.7</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="M43" t="n">
         <v>0.8936170212765957</v>
       </c>
       <c r="N43" t="n">
-        <v>0.7850467289719626</v>
+        <v>0.7887323943661972</v>
       </c>
       <c r="O43" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P43" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -3991,43 +3991,43 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G44" t="n">
-        <v>0.8072916666666666</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8072916666666666</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8854166666666666</v>
+        <v>0.8969072164948454</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7657657657657657</v>
+        <v>0.7837837837837838</v>
       </c>
       <c r="K44" t="n">
-        <v>0.8212560386473429</v>
+        <v>0.8365384615384617</v>
       </c>
       <c r="L44" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7473684210526316</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8641975308641975</v>
+        <v>0.8765432098765432</v>
       </c>
       <c r="N44" t="n">
-        <v>0.7909604519774011</v>
+        <v>0.8068181818181818</v>
       </c>
       <c r="O44" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P44" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Q44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R44" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45">
@@ -4049,37 +4049,37 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G45" t="n">
-        <v>0.859375</v>
+        <v>0.875</v>
       </c>
       <c r="H45" t="n">
-        <v>0.859375</v>
+        <v>0.875</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8617021276595744</v>
+        <v>0.865979381443299</v>
       </c>
       <c r="J45" t="n">
-        <v>0.8526315789473684</v>
+        <v>0.8842105263157894</v>
       </c>
       <c r="K45" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.8749999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8842105263157894</v>
       </c>
       <c r="M45" t="n">
         <v>0.865979381443299</v>
       </c>
       <c r="N45" t="n">
-        <v>0.8615384615384615</v>
+        <v>0.8749999999999999</v>
       </c>
       <c r="O45" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="P45" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q45" t="n">
         <v>13</v>
@@ -4107,43 +4107,43 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G46" t="n">
-        <v>0.8489583333333334</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="H46" t="n">
-        <v>0.8489583333333334</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8613861386138614</v>
+        <v>0.8252427184466019</v>
       </c>
       <c r="J46" t="n">
-        <v>0.8529411764705882</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K46" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.8292682926829268</v>
       </c>
       <c r="L46" t="n">
-        <v>0.8351648351648352</v>
+        <v>0.8089887640449438</v>
       </c>
       <c r="M46" t="n">
-        <v>0.8444444444444444</v>
+        <v>0.8</v>
       </c>
       <c r="N46" t="n">
-        <v>0.839779005524862</v>
+        <v>0.8044692737430168</v>
       </c>
       <c r="O46" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P46" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R46" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47">
@@ -4165,43 +4165,43 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="G47" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.765625</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.765625</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8210526315789474</v>
+        <v>0.7872340425531915</v>
       </c>
       <c r="J47" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.7474747474747475</v>
       </c>
       <c r="K47" t="n">
-        <v>0.8041237113402062</v>
+        <v>0.766839378238342</v>
       </c>
       <c r="L47" t="n">
-        <v>0.7835051546391752</v>
+        <v>0.7448979591836735</v>
       </c>
       <c r="M47" t="n">
-        <v>0.8172043010752689</v>
+        <v>0.7849462365591398</v>
       </c>
       <c r="N47" t="n">
-        <v>0.8</v>
+        <v>0.7643979057591623</v>
       </c>
       <c r="O47" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P47" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q47" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R47" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48">
@@ -4223,37 +4223,37 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G48" t="n">
-        <v>0.7447916666666666</v>
+        <v>0.75</v>
       </c>
       <c r="H48" t="n">
-        <v>0.7447916666666666</v>
+        <v>0.75</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="J48" t="n">
-        <v>0.6881720430107527</v>
+        <v>0.6989247311827957</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7231638418079096</v>
+        <v>0.7303370786516853</v>
       </c>
       <c r="L48" t="n">
-        <v>0.7314814814814815</v>
+        <v>0.7383177570093458</v>
       </c>
       <c r="M48" t="n">
         <v>0.797979797979798</v>
       </c>
       <c r="N48" t="n">
-        <v>0.7632850241545894</v>
+        <v>0.766990291262136</v>
       </c>
       <c r="O48" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P48" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q48" t="n">
         <v>20</v>
@@ -4281,43 +4281,43 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="G49" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7951807228915663</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="J49" t="n">
-        <v>0.7586206896551724</v>
+        <v>0.735632183908046</v>
       </c>
       <c r="K49" t="n">
-        <v>0.7764705882352942</v>
+        <v>0.7314285714285715</v>
       </c>
       <c r="L49" t="n">
-        <v>0.8073394495412844</v>
+        <v>0.7788461538461539</v>
       </c>
       <c r="M49" t="n">
-        <v>0.8380952380952381</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="N49" t="n">
-        <v>0.8224299065420561</v>
+        <v>0.7751196172248804</v>
       </c>
       <c r="O49" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P49" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q49" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R49" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50">
@@ -4339,43 +4339,43 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="G50" t="n">
-        <v>0.875</v>
+        <v>0.8385416666666666</v>
       </c>
       <c r="H50" t="n">
-        <v>0.875</v>
+        <v>0.8385416666666666</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8352941176470589</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8068181818181818</v>
       </c>
       <c r="K50" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.8208092485549133</v>
       </c>
       <c r="L50" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8411214953271028</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="N50" t="n">
-        <v>0.8799999999999999</v>
+        <v>0.8530805687203792</v>
       </c>
       <c r="O50" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="P50" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Q50" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R50" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51">
@@ -4397,37 +4397,37 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G51" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.8854166666666666</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.8854166666666666</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8777777777777778</v>
+        <v>0.875</v>
       </c>
       <c r="J51" t="n">
-        <v>0.8977272727272727</v>
+        <v>0.875</v>
       </c>
       <c r="K51" t="n">
-        <v>0.8876404494382022</v>
+        <v>0.875</v>
       </c>
       <c r="L51" t="n">
-        <v>0.9117647058823529</v>
+        <v>0.8942307692307693</v>
       </c>
       <c r="M51" t="n">
         <v>0.8942307692307693</v>
       </c>
       <c r="N51" t="n">
-        <v>0.9029126213592232</v>
+        <v>0.8942307692307693</v>
       </c>
       <c r="O51" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P51" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q51" t="n">
         <v>11</v>
@@ -4455,43 +4455,43 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G52" t="n">
-        <v>0.8489583333333334</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8489583333333334</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8809523809523809</v>
+        <v>0.8536585365853658</v>
       </c>
       <c r="J52" t="n">
-        <v>0.7956989247311828</v>
+        <v>0.7526881720430108</v>
       </c>
       <c r="K52" t="n">
-        <v>0.8361581920903954</v>
+        <v>0.8</v>
       </c>
       <c r="L52" t="n">
-        <v>0.8240740740740741</v>
+        <v>0.7909090909090909</v>
       </c>
       <c r="M52" t="n">
-        <v>0.898989898989899</v>
+        <v>0.8787878787878788</v>
       </c>
       <c r="N52" t="n">
-        <v>0.859903381642512</v>
+        <v>0.8325358851674641</v>
       </c>
       <c r="O52" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P52" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q52" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R52" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53">
@@ -4513,43 +4513,43 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="G53" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="H53" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8160919540229885</v>
+        <v>0.7640449438202247</v>
       </c>
       <c r="J53" t="n">
-        <v>0.7473684210526316</v>
+        <v>0.7157894736842105</v>
       </c>
       <c r="K53" t="n">
-        <v>0.7802197802197802</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="L53" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.7378640776699029</v>
       </c>
       <c r="M53" t="n">
-        <v>0.8350515463917526</v>
+        <v>0.7835051546391752</v>
       </c>
       <c r="N53" t="n">
-        <v>0.801980198019802</v>
+        <v>0.7600000000000001</v>
       </c>
       <c r="O53" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P53" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q53" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R53" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54">
@@ -4571,43 +4571,43 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G54" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="H54" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="I54" t="n">
-        <v>0.7731958762886598</v>
+        <v>0.7920792079207921</v>
       </c>
       <c r="J54" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.8080808080808081</v>
       </c>
       <c r="K54" t="n">
-        <v>0.7653061224489796</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>0.7473684210526316</v>
+        <v>0.7912087912087912</v>
       </c>
       <c r="M54" t="n">
-        <v>0.7634408602150538</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="N54" t="n">
-        <v>0.7553191489361704</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="O54" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="P54" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Q54" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R54" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55">
@@ -4629,31 +4629,31 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G55" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="H55" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8289473684210527</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="J55" t="n">
         <v>0.7</v>
       </c>
       <c r="K55" t="n">
-        <v>0.7590361445783133</v>
+        <v>0.7544910179640719</v>
       </c>
       <c r="L55" t="n">
-        <v>0.7672413793103449</v>
+        <v>0.7652173913043478</v>
       </c>
       <c r="M55" t="n">
-        <v>0.8725490196078431</v>
+        <v>0.8627450980392157</v>
       </c>
       <c r="N55" t="n">
-        <v>0.8165137614678899</v>
+        <v>0.8110599078341014</v>
       </c>
       <c r="O55" t="n">
         <v>63</v>
@@ -4662,10 +4662,10 @@
         <v>27</v>
       </c>
       <c r="Q55" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R55" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56">
@@ -4687,43 +4687,43 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G56" t="n">
-        <v>0.84375</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="H56" t="n">
-        <v>0.84375</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8478260869565217</v>
+        <v>0.8260869565217391</v>
       </c>
       <c r="J56" t="n">
-        <v>0.8297872340425532</v>
+        <v>0.8085106382978723</v>
       </c>
       <c r="K56" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.8172043010752688</v>
       </c>
       <c r="L56" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="N56" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.8282828282828283</v>
       </c>
       <c r="O56" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P56" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q56" t="n">
         <v>16</v>
       </c>
-      <c r="Q56" t="n">
-        <v>14</v>
-      </c>
       <c r="R56" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57">
@@ -4745,43 +4745,43 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G57" t="n">
-        <v>0.8489583333333334</v>
+        <v>0.84375</v>
       </c>
       <c r="H57" t="n">
-        <v>0.8489583333333334</v>
+        <v>0.84375</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.9220779220779221</v>
       </c>
       <c r="J57" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.7473684210526316</v>
       </c>
       <c r="K57" t="n">
-        <v>0.8379888268156424</v>
+        <v>0.8255813953488372</v>
       </c>
       <c r="L57" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.7913043478260869</v>
       </c>
       <c r="M57" t="n">
-        <v>0.9072164948453608</v>
+        <v>0.9381443298969072</v>
       </c>
       <c r="N57" t="n">
-        <v>0.8585365853658536</v>
+        <v>0.8584905660377358</v>
       </c>
       <c r="O57" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="P57" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Q57" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R57" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58">
@@ -4803,43 +4803,43 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G58" t="n">
-        <v>0.8697916666666666</v>
+        <v>0.8802083333333334</v>
       </c>
       <c r="H58" t="n">
-        <v>0.8697916666666666</v>
+        <v>0.8802083333333334</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8586956521739131</v>
+        <v>0.8863636363636364</v>
       </c>
       <c r="J58" t="n">
-        <v>0.8681318681318682</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="K58" t="n">
-        <v>0.8633879781420766</v>
+        <v>0.8715083798882681</v>
       </c>
       <c r="L58" t="n">
-        <v>0.88</v>
+        <v>0.875</v>
       </c>
       <c r="M58" t="n">
-        <v>0.8712871287128713</v>
+        <v>0.900990099009901</v>
       </c>
       <c r="N58" t="n">
-        <v>0.8756218905472637</v>
+        <v>0.8878048780487806</v>
       </c>
       <c r="O58" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q58" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="R58" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59">
@@ -4870,34 +4870,34 @@
         <v>0.828125</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7956989247311828</v>
+        <v>0.8021978021978022</v>
       </c>
       <c r="J59" t="n">
-        <v>0.8409090909090909</v>
+        <v>0.8295454545454546</v>
       </c>
       <c r="K59" t="n">
-        <v>0.8176795580110496</v>
+        <v>0.8156424581005587</v>
       </c>
       <c r="L59" t="n">
-        <v>0.8585858585858586</v>
+        <v>0.8514851485148515</v>
       </c>
       <c r="M59" t="n">
-        <v>0.8173076923076923</v>
+        <v>0.8269230769230769</v>
       </c>
       <c r="N59" t="n">
-        <v>0.8374384236453203</v>
+        <v>0.8390243902439023</v>
       </c>
       <c r="O59" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P59" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q59" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R59" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="60">
@@ -4919,43 +4919,43 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8229166666666666</v>
+        <v>0.8125</v>
       </c>
       <c r="H60" t="n">
-        <v>0.8229166666666666</v>
+        <v>0.8125</v>
       </c>
       <c r="I60" t="n">
-        <v>0.9052631578947369</v>
+        <v>0.9120879120879121</v>
       </c>
       <c r="J60" t="n">
-        <v>0.7747747747747747</v>
+        <v>0.7477477477477478</v>
       </c>
       <c r="K60" t="n">
-        <v>0.8349514563106797</v>
+        <v>0.8217821782178218</v>
       </c>
       <c r="L60" t="n">
-        <v>0.7422680412371134</v>
+        <v>0.7227722772277227</v>
       </c>
       <c r="M60" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9012345679012346</v>
       </c>
       <c r="N60" t="n">
-        <v>0.8089887640449438</v>
+        <v>0.8021978021978022</v>
       </c>
       <c r="O60" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P60" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R60" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61">
@@ -4977,43 +4977,43 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G61" t="n">
-        <v>0.765625</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="H61" t="n">
-        <v>0.765625</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="I61" t="n">
-        <v>0.7731958762886598</v>
+        <v>0.8191489361702128</v>
       </c>
       <c r="J61" t="n">
-        <v>0.7653061224489796</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="K61" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.8020833333333333</v>
       </c>
       <c r="L61" t="n">
-        <v>0.7578947368421053</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="M61" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.8191489361702128</v>
       </c>
       <c r="N61" t="n">
-        <v>0.761904761904762</v>
+        <v>0.8020833333333333</v>
       </c>
       <c r="O61" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P61" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q61" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="R61" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62">
@@ -5035,31 +5035,31 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G62" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H62" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8514851485148515</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="J62" t="n">
         <v>0.8113207547169812</v>
       </c>
       <c r="K62" t="n">
-        <v>0.8309178743961353</v>
+        <v>0.8431372549019608</v>
       </c>
       <c r="L62" t="n">
-        <v>0.7802197802197802</v>
+        <v>0.7872340425531915</v>
       </c>
       <c r="M62" t="n">
-        <v>0.8255813953488372</v>
+        <v>0.8604651162790697</v>
       </c>
       <c r="N62" t="n">
-        <v>0.8022598870056498</v>
+        <v>0.8222222222222222</v>
       </c>
       <c r="O62" t="n">
         <v>86</v>
@@ -5068,10 +5068,10 @@
         <v>20</v>
       </c>
       <c r="Q62" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="R62" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63">
@@ -5093,43 +5093,43 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G63" t="n">
-        <v>0.765625</v>
+        <v>0.78125</v>
       </c>
       <c r="H63" t="n">
-        <v>0.765625</v>
+        <v>0.78125</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7792207792207793</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="J63" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.7045454545454546</v>
       </c>
       <c r="K63" t="n">
-        <v>0.7272727272727272</v>
+        <v>0.746987951807229</v>
       </c>
       <c r="L63" t="n">
-        <v>0.7565217391304347</v>
+        <v>0.7719298245614035</v>
       </c>
       <c r="M63" t="n">
-        <v>0.8365384615384616</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="N63" t="n">
-        <v>0.7945205479452055</v>
+        <v>0.8073394495412844</v>
       </c>
       <c r="O63" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P63" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q63" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R63" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="64">
@@ -5151,31 +5151,31 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G64" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="H64" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8051948051948052</v>
+        <v>0.7654320987654321</v>
       </c>
       <c r="J64" t="n">
         <v>0.6813186813186813</v>
       </c>
       <c r="K64" t="n">
-        <v>0.7380952380952381</v>
+        <v>0.7209302325581395</v>
       </c>
       <c r="L64" t="n">
-        <v>0.7478260869565218</v>
+        <v>0.7387387387387387</v>
       </c>
       <c r="M64" t="n">
-        <v>0.8514851485148515</v>
+        <v>0.8118811881188119</v>
       </c>
       <c r="N64" t="n">
-        <v>0.7962962962962963</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="O64" t="n">
         <v>62</v>
@@ -5184,10 +5184,10 @@
         <v>29</v>
       </c>
       <c r="Q64" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="R64" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65">
@@ -5209,43 +5209,43 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G65" t="n">
-        <v>0.8125</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="H65" t="n">
-        <v>0.8125</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8470588235294118</v>
+        <v>0.8352941176470589</v>
       </c>
       <c r="J65" t="n">
-        <v>0.7578947368421053</v>
+        <v>0.7473684210526316</v>
       </c>
       <c r="K65" t="n">
-        <v>0.8</v>
+        <v>0.7888888888888889</v>
       </c>
       <c r="L65" t="n">
-        <v>0.7850467289719626</v>
+        <v>0.7757009345794392</v>
       </c>
       <c r="M65" t="n">
-        <v>0.865979381443299</v>
+        <v>0.8556701030927835</v>
       </c>
       <c r="N65" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.8137254901960783</v>
       </c>
       <c r="O65" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P65" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q65" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R65" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66">
@@ -5267,37 +5267,37 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G66" t="n">
-        <v>0.8645833333333334</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="H66" t="n">
-        <v>0.8645833333333334</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8433734939759037</v>
+        <v>0.8395061728395061</v>
       </c>
       <c r="J66" t="n">
-        <v>0.8433734939759037</v>
+        <v>0.8192771084337349</v>
       </c>
       <c r="K66" t="n">
-        <v>0.8433734939759037</v>
+        <v>0.8292682926829269</v>
       </c>
       <c r="L66" t="n">
-        <v>0.8807339449541285</v>
+        <v>0.8648648648648649</v>
       </c>
       <c r="M66" t="n">
         <v>0.8807339449541285</v>
       </c>
       <c r="N66" t="n">
-        <v>0.8807339449541285</v>
+        <v>0.8727272727272727</v>
       </c>
       <c r="O66" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P66" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q66" t="n">
         <v>13</v>
@@ -5325,43 +5325,43 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G67" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="H67" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8313253012048193</v>
       </c>
       <c r="J67" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.75</v>
       </c>
       <c r="K67" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7885714285714285</v>
       </c>
       <c r="L67" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.7889908256880734</v>
       </c>
       <c r="M67" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="N67" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8229665071770336</v>
       </c>
       <c r="O67" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P67" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q67" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R67" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68">
@@ -5383,31 +5383,31 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G68" t="n">
-        <v>0.78125</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="H68" t="n">
-        <v>0.78125</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.8279569892473119</v>
       </c>
       <c r="J68" t="n">
         <v>0.7857142857142857</v>
       </c>
       <c r="K68" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.806282722513089</v>
       </c>
       <c r="L68" t="n">
-        <v>0.776595744680851</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="M68" t="n">
-        <v>0.776595744680851</v>
+        <v>0.8297872340425532</v>
       </c>
       <c r="N68" t="n">
-        <v>0.776595744680851</v>
+        <v>0.8082901554404145</v>
       </c>
       <c r="O68" t="n">
         <v>77</v>
@@ -5416,10 +5416,10 @@
         <v>21</v>
       </c>
       <c r="Q68" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="R68" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="69">
@@ -5441,43 +5441,43 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G69" t="n">
-        <v>0.828125</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H69" t="n">
-        <v>0.828125</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8588235294117647</v>
+        <v>0.8974358974358975</v>
       </c>
       <c r="J69" t="n">
-        <v>0.776595744680851</v>
+        <v>0.7446808510638298</v>
       </c>
       <c r="K69" t="n">
-        <v>0.8156424581005587</v>
+        <v>0.813953488372093</v>
       </c>
       <c r="L69" t="n">
-        <v>0.8037383177570093</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="M69" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.9183673469387755</v>
       </c>
       <c r="N69" t="n">
-        <v>0.8390243902439024</v>
+        <v>0.8490566037735849</v>
       </c>
       <c r="O69" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="P69" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q69" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="R69" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70">
@@ -5499,37 +5499,37 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G70" t="n">
-        <v>0.8645833333333334</v>
+        <v>0.859375</v>
       </c>
       <c r="H70" t="n">
-        <v>0.8645833333333334</v>
+        <v>0.859375</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8607594936708861</v>
+        <v>0.8589743589743589</v>
       </c>
       <c r="J70" t="n">
-        <v>0.8192771084337349</v>
+        <v>0.8072289156626506</v>
       </c>
       <c r="K70" t="n">
-        <v>0.8395061728395061</v>
+        <v>0.8322981366459627</v>
       </c>
       <c r="L70" t="n">
-        <v>0.8672566371681416</v>
+        <v>0.8596491228070176</v>
       </c>
       <c r="M70" t="n">
         <v>0.8990825688073395</v>
       </c>
       <c r="N70" t="n">
-        <v>0.8828828828828829</v>
+        <v>0.8789237668161435</v>
       </c>
       <c r="O70" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P70" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q70" t="n">
         <v>11</v>
@@ -5557,43 +5557,43 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G71" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.8125</v>
       </c>
       <c r="H71" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.8125</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8780487804878049</v>
+        <v>0.8433734939759037</v>
       </c>
       <c r="J71" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.7526881720430108</v>
       </c>
       <c r="K71" t="n">
-        <v>0.8228571428571428</v>
+        <v>0.7954545454545455</v>
       </c>
       <c r="L71" t="n">
-        <v>0.8090909090909091</v>
+        <v>0.7889908256880734</v>
       </c>
       <c r="M71" t="n">
-        <v>0.898989898989899</v>
+        <v>0.8686868686868687</v>
       </c>
       <c r="N71" t="n">
-        <v>0.8516746411483254</v>
+        <v>0.8269230769230771</v>
       </c>
       <c r="O71" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P71" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q71" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R71" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="72">
@@ -5615,43 +5615,43 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G72" t="n">
-        <v>0.796875</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="H72" t="n">
-        <v>0.796875</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8369565217391305</v>
+        <v>0.8586956521739131</v>
       </c>
       <c r="J72" t="n">
-        <v>0.7623762376237624</v>
+        <v>0.7821782178217822</v>
       </c>
       <c r="K72" t="n">
-        <v>0.7979274611398964</v>
+        <v>0.8186528497409327</v>
       </c>
       <c r="L72" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="M72" t="n">
-        <v>0.8351648351648352</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="N72" t="n">
-        <v>0.7958115183246074</v>
+        <v>0.8167539267015708</v>
       </c>
       <c r="O72" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P72" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q72" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R72" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73">
@@ -5682,34 +5682,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8686868686868687</v>
+        <v>0.8613861386138614</v>
       </c>
       <c r="J73" t="n">
-        <v>0.819047619047619</v>
+        <v>0.8285714285714286</v>
       </c>
       <c r="K73" t="n">
-        <v>0.8431372549019608</v>
+        <v>0.8446601941747574</v>
       </c>
       <c r="L73" t="n">
-        <v>0.7956989247311828</v>
+        <v>0.8021978021978022</v>
       </c>
       <c r="M73" t="n">
-        <v>0.8505747126436781</v>
+        <v>0.8390804597701149</v>
       </c>
       <c r="N73" t="n">
-        <v>0.8222222222222222</v>
+        <v>0.8202247191011236</v>
       </c>
       <c r="O73" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P73" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q73" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R73" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="74">
@@ -5731,43 +5731,43 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G74" t="n">
-        <v>0.78125</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="H74" t="n">
-        <v>0.78125</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7625</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="J74" t="n">
-        <v>0.7261904761904762</v>
+        <v>0.6904761904761905</v>
       </c>
       <c r="K74" t="n">
-        <v>0.7439024390243903</v>
+        <v>0.725</v>
       </c>
       <c r="L74" t="n">
-        <v>0.7946428571428571</v>
+        <v>0.7758620689655172</v>
       </c>
       <c r="M74" t="n">
-        <v>0.8240740740740741</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N74" t="n">
-        <v>0.809090909090909</v>
+        <v>0.8035714285714286</v>
       </c>
       <c r="O74" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="P74" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q74" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R74" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="75">
@@ -5789,43 +5789,43 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="G75" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="H75" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8717948717948718</v>
+        <v>0.7951807228915663</v>
       </c>
       <c r="J75" t="n">
-        <v>0.6868686868686869</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K75" t="n">
-        <v>0.768361581920904</v>
+        <v>0.7252747252747251</v>
       </c>
       <c r="L75" t="n">
-        <v>0.7280701754385965</v>
+        <v>0.6972477064220184</v>
       </c>
       <c r="M75" t="n">
-        <v>0.8924731182795699</v>
+        <v>0.8172043010752689</v>
       </c>
       <c r="N75" t="n">
-        <v>0.8019323671497586</v>
+        <v>0.7524752475247526</v>
       </c>
       <c r="O75" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P75" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q75" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="R75" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="76">
@@ -5847,43 +5847,43 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G76" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8385416666666666</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8385416666666666</v>
       </c>
       <c r="I76" t="n">
-        <v>0.898876404494382</v>
+        <v>0.8863636363636364</v>
       </c>
       <c r="J76" t="n">
-        <v>0.8080808080808081</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="K76" t="n">
-        <v>0.851063829787234</v>
+        <v>0.8342245989304813</v>
       </c>
       <c r="L76" t="n">
-        <v>0.8155339805825242</v>
+        <v>0.7980769230769231</v>
       </c>
       <c r="M76" t="n">
-        <v>0.9032258064516129</v>
+        <v>0.8924731182795699</v>
       </c>
       <c r="N76" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8426395939086294</v>
       </c>
       <c r="O76" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P76" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R76" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77">
@@ -5905,37 +5905,37 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G77" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.796875</v>
       </c>
       <c r="H77" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.796875</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8314606741573034</v>
+        <v>0.8295454545454546</v>
       </c>
       <c r="J77" t="n">
-        <v>0.7628865979381443</v>
+        <v>0.7525773195876289</v>
       </c>
       <c r="K77" t="n">
-        <v>0.7956989247311828</v>
+        <v>0.7891891891891891</v>
       </c>
       <c r="L77" t="n">
-        <v>0.7766990291262136</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="M77" t="n">
         <v>0.8421052631578947</v>
       </c>
       <c r="N77" t="n">
-        <v>0.8080808080808081</v>
+        <v>0.8040201005025126</v>
       </c>
       <c r="O77" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P77" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q77" t="n">
         <v>15</v>
@@ -5963,43 +5963,43 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8697916666666666</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="H78" t="n">
-        <v>0.8697916666666666</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8706896551724138</v>
+        <v>0.8547008547008547</v>
       </c>
       <c r="J78" t="n">
-        <v>0.9099099099099099</v>
+        <v>0.9009009009009009</v>
       </c>
       <c r="K78" t="n">
-        <v>0.8898678414096917</v>
+        <v>0.8771929824561403</v>
       </c>
       <c r="L78" t="n">
-        <v>0.868421052631579</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="M78" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.7901234567901234</v>
       </c>
       <c r="N78" t="n">
-        <v>0.8407643312101911</v>
+        <v>0.8205128205128205</v>
       </c>
       <c r="O78" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P78" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q78" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R78" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="79">
@@ -6021,31 +6021,31 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G79" t="n">
-        <v>0.84375</v>
+        <v>0.8489583333333334</v>
       </c>
       <c r="H79" t="n">
-        <v>0.84375</v>
+        <v>0.8489583333333334</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8902439024390244</v>
+        <v>0.9012345679012346</v>
       </c>
       <c r="J79" t="n">
         <v>0.776595744680851</v>
       </c>
       <c r="K79" t="n">
-        <v>0.8295454545454545</v>
+        <v>0.8342857142857142</v>
       </c>
       <c r="L79" t="n">
-        <v>0.8090909090909091</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="M79" t="n">
-        <v>0.9081632653061225</v>
+        <v>0.9183673469387755</v>
       </c>
       <c r="N79" t="n">
-        <v>0.8557692307692307</v>
+        <v>0.861244019138756</v>
       </c>
       <c r="O79" t="n">
         <v>73</v>
@@ -6054,10 +6054,10 @@
         <v>21</v>
       </c>
       <c r="Q79" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R79" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="80">
@@ -6088,34 +6088,34 @@
         <v>0.765625</v>
       </c>
       <c r="I80" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="J80" t="n">
-        <v>0.7586206896551724</v>
+        <v>0.735632183908046</v>
       </c>
       <c r="K80" t="n">
-        <v>0.7457627118644068</v>
+        <v>0.7398843930635838</v>
       </c>
       <c r="L80" t="n">
-        <v>0.7941176470588235</v>
+        <v>0.7830188679245284</v>
       </c>
       <c r="M80" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.7904761904761904</v>
       </c>
       <c r="N80" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.7867298578199052</v>
       </c>
       <c r="O80" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P80" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q80" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R80" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="81">
@@ -6137,43 +6137,43 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G81" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="H81" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="I81" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.8227848101265823</v>
       </c>
       <c r="J81" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.7065217391304348</v>
       </c>
       <c r="K81" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7602339181286549</v>
       </c>
       <c r="L81" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.7610619469026548</v>
       </c>
       <c r="M81" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="N81" t="n">
-        <v>0.7843137254901961</v>
+        <v>0.8075117370892019</v>
       </c>
       <c r="O81" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="P81" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q81" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="R81" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="82">
@@ -6195,37 +6195,37 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="G82" t="n">
-        <v>0.7447916666666666</v>
+        <v>0.7135416666666666</v>
       </c>
       <c r="H82" t="n">
-        <v>0.7447916666666666</v>
+        <v>0.7135416666666666</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7397260273972602</v>
+        <v>0.7164179104477612</v>
       </c>
       <c r="J82" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="K82" t="n">
-        <v>0.6878980891719746</v>
+        <v>0.6357615894039734</v>
       </c>
       <c r="L82" t="n">
-        <v>0.7478991596638656</v>
+        <v>0.712</v>
       </c>
       <c r="M82" t="n">
         <v>0.8240740740740741</v>
       </c>
       <c r="N82" t="n">
-        <v>0.7841409691629956</v>
+        <v>0.7639484978540771</v>
       </c>
       <c r="O82" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="P82" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Q82" t="n">
         <v>19</v>
@@ -6253,37 +6253,37 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G83" t="n">
-        <v>0.828125</v>
+        <v>0.84375</v>
       </c>
       <c r="H83" t="n">
-        <v>0.828125</v>
+        <v>0.84375</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8674698795180723</v>
+        <v>0.8720930232558139</v>
       </c>
       <c r="J83" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.7978723404255319</v>
       </c>
       <c r="K83" t="n">
-        <v>0.8135593220338984</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L83" t="n">
-        <v>0.7981651376146789</v>
+        <v>0.8207547169811321</v>
       </c>
       <c r="M83" t="n">
         <v>0.8877551020408163</v>
       </c>
       <c r="N83" t="n">
-        <v>0.8405797101449275</v>
+        <v>0.8529411764705883</v>
       </c>
       <c r="O83" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="P83" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q83" t="n">
         <v>11</v>
@@ -6311,31 +6311,31 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G84" t="n">
-        <v>0.8489583333333334</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="H84" t="n">
-        <v>0.8489583333333334</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="I84" t="n">
-        <v>0.9111111111111111</v>
+        <v>0.9213483146067416</v>
       </c>
       <c r="J84" t="n">
         <v>0.7961165048543689</v>
       </c>
       <c r="K84" t="n">
-        <v>0.8497409326424871</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="L84" t="n">
-        <v>0.7941176470588235</v>
+        <v>0.7961165048543689</v>
       </c>
       <c r="M84" t="n">
-        <v>0.9101123595505618</v>
+        <v>0.9213483146067416</v>
       </c>
       <c r="N84" t="n">
-        <v>0.8481675392670156</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="O84" t="n">
         <v>82</v>
@@ -6344,10 +6344,10 @@
         <v>21</v>
       </c>
       <c r="Q84" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R84" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85">
@@ -6369,31 +6369,31 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G85" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.765625</v>
       </c>
       <c r="H85" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.765625</v>
       </c>
       <c r="I85" t="n">
-        <v>0.8202247191011236</v>
+        <v>0.8690476190476191</v>
       </c>
       <c r="J85" t="n">
         <v>0.6822429906542056</v>
       </c>
       <c r="K85" t="n">
-        <v>0.7448979591836734</v>
+        <v>0.7643979057591622</v>
       </c>
       <c r="L85" t="n">
-        <v>0.6699029126213593</v>
+        <v>0.6851851851851852</v>
       </c>
       <c r="M85" t="n">
-        <v>0.8117647058823529</v>
+        <v>0.8705882352941177</v>
       </c>
       <c r="N85" t="n">
-        <v>0.7340425531914895</v>
+        <v>0.766839378238342</v>
       </c>
       <c r="O85" t="n">
         <v>73</v>
@@ -6402,10 +6402,10 @@
         <v>34</v>
       </c>
       <c r="Q85" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="R85" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="86">
@@ -6427,43 +6427,43 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G86" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H86" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I86" t="n">
-        <v>0.8367346938775511</v>
+        <v>0.8556701030927835</v>
       </c>
       <c r="J86" t="n">
-        <v>0.8118811881188119</v>
+        <v>0.8217821782178217</v>
       </c>
       <c r="K86" t="n">
-        <v>0.8241206030150754</v>
+        <v>0.8383838383838383</v>
       </c>
       <c r="L86" t="n">
-        <v>0.7978723404255319</v>
+        <v>0.8105263157894737</v>
       </c>
       <c r="M86" t="n">
-        <v>0.8241758241758241</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="N86" t="n">
-        <v>0.8108108108108109</v>
+        <v>0.8279569892473119</v>
       </c>
       <c r="O86" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P86" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q86" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R86" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="87">
@@ -6485,37 +6485,37 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G87" t="n">
-        <v>0.8802083333333334</v>
+        <v>0.8854166666666666</v>
       </c>
       <c r="H87" t="n">
-        <v>0.8802083333333334</v>
+        <v>0.8854166666666666</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8854166666666666</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="J87" t="n">
-        <v>0.8762886597938144</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="K87" t="n">
-        <v>0.8808290155440415</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="L87" t="n">
-        <v>0.875</v>
+        <v>0.8842105263157894</v>
       </c>
       <c r="M87" t="n">
         <v>0.8842105263157894</v>
       </c>
       <c r="N87" t="n">
-        <v>0.8795811518324607</v>
+        <v>0.8842105263157894</v>
       </c>
       <c r="O87" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P87" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q87" t="n">
         <v>11</v>
@@ -6543,43 +6543,43 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G88" t="n">
-        <v>0.796875</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="H88" t="n">
-        <v>0.796875</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8229166666666666</v>
+        <v>0.8080808080808081</v>
       </c>
       <c r="J88" t="n">
-        <v>0.7821782178217822</v>
+        <v>0.7920792079207921</v>
       </c>
       <c r="K88" t="n">
-        <v>0.8020304568527918</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L88" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="M88" t="n">
-        <v>0.8131868131868132</v>
+        <v>0.7912087912087912</v>
       </c>
       <c r="N88" t="n">
-        <v>0.7914438502673797</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="O88" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P88" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q88" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R88" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="89">
@@ -6601,43 +6601,43 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="G89" t="n">
-        <v>0.8072916666666666</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="H89" t="n">
-        <v>0.8072916666666666</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="I89" t="n">
-        <v>0.851063829787234</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="J89" t="n">
-        <v>0.7766990291262136</v>
+        <v>0.7087378640776699</v>
       </c>
       <c r="K89" t="n">
-        <v>0.8121827411167513</v>
+        <v>0.756476683937824</v>
       </c>
       <c r="L89" t="n">
-        <v>0.7653061224489796</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="M89" t="n">
-        <v>0.8426966292134831</v>
+        <v>0.8089887640449438</v>
       </c>
       <c r="N89" t="n">
-        <v>0.8021390374331551</v>
+        <v>0.7539267015706808</v>
       </c>
       <c r="O89" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="P89" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="Q89" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R89" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="90">
@@ -6659,31 +6659,31 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G90" t="n">
-        <v>0.8229166666666666</v>
+        <v>0.8125</v>
       </c>
       <c r="H90" t="n">
-        <v>0.8229166666666666</v>
+        <v>0.8125</v>
       </c>
       <c r="I90" t="n">
-        <v>0.875</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="J90" t="n">
         <v>0.77</v>
       </c>
       <c r="K90" t="n">
-        <v>0.8191489361702129</v>
+        <v>0.8105263157894737</v>
       </c>
       <c r="L90" t="n">
-        <v>0.7788461538461539</v>
+        <v>0.7745098039215687</v>
       </c>
       <c r="M90" t="n">
-        <v>0.8804347826086957</v>
+        <v>0.8586956521739131</v>
       </c>
       <c r="N90" t="n">
-        <v>0.826530612244898</v>
+        <v>0.8144329896907218</v>
       </c>
       <c r="O90" t="n">
         <v>77</v>
@@ -6692,10 +6692,10 @@
         <v>23</v>
       </c>
       <c r="Q90" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R90" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91">
@@ -6717,43 +6717,43 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G91" t="n">
-        <v>0.8072916666666666</v>
+        <v>0.796875</v>
       </c>
       <c r="H91" t="n">
-        <v>0.8072916666666666</v>
+        <v>0.796875</v>
       </c>
       <c r="I91" t="n">
-        <v>0.8863636363636364</v>
+        <v>0.875</v>
       </c>
       <c r="J91" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="K91" t="n">
-        <v>0.8082901554404146</v>
+        <v>0.7979274611398963</v>
       </c>
       <c r="L91" t="n">
-        <v>0.7403846153846154</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="M91" t="n">
-        <v>0.8850574712643678</v>
+        <v>0.8735632183908046</v>
       </c>
       <c r="N91" t="n">
-        <v>0.8062827225130891</v>
+        <v>0.7958115183246074</v>
       </c>
       <c r="O91" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P91" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q91" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R91" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="92">
@@ -6775,43 +6775,43 @@
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="G92" t="n">
-        <v>0.8125</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="H92" t="n">
-        <v>0.8125</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8125</v>
+        <v>0.8679245283018868</v>
       </c>
       <c r="J92" t="n">
-        <v>0.8584905660377359</v>
+        <v>0.8679245283018868</v>
       </c>
       <c r="K92" t="n">
-        <v>0.8348623853211008</v>
+        <v>0.8679245283018869</v>
       </c>
       <c r="L92" t="n">
-        <v>0.8125</v>
+        <v>0.8372093023255814</v>
       </c>
       <c r="M92" t="n">
-        <v>0.7558139534883721</v>
+        <v>0.8372093023255814</v>
       </c>
       <c r="N92" t="n">
-        <v>0.783132530120482</v>
+        <v>0.8372093023255814</v>
       </c>
       <c r="O92" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P92" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q92" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="R92" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93">
@@ -6833,43 +6833,43 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G93" t="n">
-        <v>0.828125</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H93" t="n">
-        <v>0.828125</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9080459770114943</v>
       </c>
       <c r="J93" t="n">
-        <v>0.7766990291262136</v>
+        <v>0.7669902912621359</v>
       </c>
       <c r="K93" t="n">
-        <v>0.8290155440414507</v>
+        <v>0.8315789473684211</v>
       </c>
       <c r="L93" t="n">
-        <v>0.7745098039215687</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="M93" t="n">
-        <v>0.8876404494382022</v>
+        <v>0.9101123595505618</v>
       </c>
       <c r="N93" t="n">
-        <v>0.8272251308900522</v>
+        <v>0.8350515463917525</v>
       </c>
       <c r="O93" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P93" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q93" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R93" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94">
@@ -6891,43 +6891,43 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G94" t="n">
-        <v>0.8229166666666666</v>
+        <v>0.8125</v>
       </c>
       <c r="H94" t="n">
-        <v>0.8229166666666666</v>
+        <v>0.8125</v>
       </c>
       <c r="I94" t="n">
-        <v>0.85</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="J94" t="n">
-        <v>0.8173076923076923</v>
+        <v>0.7884615384615384</v>
       </c>
       <c r="K94" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="L94" t="n">
-        <v>0.7934782608695652</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="M94" t="n">
-        <v>0.8295454545454546</v>
+        <v>0.8409090909090909</v>
       </c>
       <c r="N94" t="n">
-        <v>0.8111111111111111</v>
+        <v>0.8043478260869567</v>
       </c>
       <c r="O94" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P94" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q94" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R94" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="95">
@@ -6949,43 +6949,43 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="G95" t="n">
-        <v>0.859375</v>
+        <v>0.828125</v>
       </c>
       <c r="H95" t="n">
-        <v>0.859375</v>
+        <v>0.828125</v>
       </c>
       <c r="I95" t="n">
-        <v>0.9156626506024096</v>
+        <v>0.8705882352941177</v>
       </c>
       <c r="J95" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="K95" t="n">
-        <v>0.8491620111731844</v>
+        <v>0.8176795580110497</v>
       </c>
       <c r="L95" t="n">
-        <v>0.8165137614678899</v>
+        <v>0.794392523364486</v>
       </c>
       <c r="M95" t="n">
-        <v>0.9270833333333334</v>
+        <v>0.8854166666666666</v>
       </c>
       <c r="N95" t="n">
-        <v>0.8682926829268294</v>
+        <v>0.8374384236453202</v>
       </c>
       <c r="O95" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P95" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q95" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R95" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="96">
@@ -7007,37 +7007,37 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G96" t="n">
-        <v>0.859375</v>
+        <v>0.8489583333333334</v>
       </c>
       <c r="H96" t="n">
-        <v>0.859375</v>
+        <v>0.8489583333333334</v>
       </c>
       <c r="I96" t="n">
-        <v>0.8941176470588236</v>
+        <v>0.8915662650602409</v>
       </c>
       <c r="J96" t="n">
-        <v>0.8085106382978723</v>
+        <v>0.7872340425531915</v>
       </c>
       <c r="K96" t="n">
-        <v>0.8491620111731844</v>
+        <v>0.8361581920903955</v>
       </c>
       <c r="L96" t="n">
-        <v>0.8317757009345794</v>
+        <v>0.8165137614678899</v>
       </c>
       <c r="M96" t="n">
         <v>0.9081632653061225</v>
       </c>
       <c r="N96" t="n">
-        <v>0.8682926829268293</v>
+        <v>0.8599033816425121</v>
       </c>
       <c r="O96" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P96" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q96" t="n">
         <v>9</v>
@@ -7065,37 +7065,37 @@
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G97" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="H97" t="n">
-        <v>0.7864583333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8271604938271605</v>
+        <v>0.825</v>
       </c>
       <c r="J97" t="n">
-        <v>0.7127659574468085</v>
+        <v>0.7021276595744681</v>
       </c>
       <c r="K97" t="n">
-        <v>0.7657142857142857</v>
+        <v>0.7586206896551724</v>
       </c>
       <c r="L97" t="n">
-        <v>0.7567567567567568</v>
+        <v>0.75</v>
       </c>
       <c r="M97" t="n">
         <v>0.8571428571428571</v>
       </c>
       <c r="N97" t="n">
-        <v>0.8038277511961723</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="O97" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P97" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q97" t="n">
         <v>14</v>
@@ -7123,43 +7123,43 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G98" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.828125</v>
       </c>
       <c r="H98" t="n">
-        <v>0.8385416666666666</v>
+        <v>0.828125</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8734177215189873</v>
+        <v>0.8352941176470589</v>
       </c>
       <c r="J98" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7888888888888889</v>
       </c>
       <c r="K98" t="n">
-        <v>0.8165680473372781</v>
+        <v>0.8114285714285714</v>
       </c>
       <c r="L98" t="n">
-        <v>0.8141592920353983</v>
+        <v>0.8224299065420561</v>
       </c>
       <c r="M98" t="n">
-        <v>0.9019607843137255</v>
+        <v>0.8627450980392157</v>
       </c>
       <c r="N98" t="n">
-        <v>0.8558139534883722</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="O98" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P98" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q98" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="R98" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="99">
@@ -7181,31 +7181,31 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G99" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.828125</v>
       </c>
       <c r="H99" t="n">
-        <v>0.8177083333333334</v>
+        <v>0.828125</v>
       </c>
       <c r="I99" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="J99" t="n">
         <v>0.7128712871287128</v>
       </c>
       <c r="K99" t="n">
-        <v>0.8044692737430168</v>
+        <v>0.8135593220338982</v>
       </c>
       <c r="L99" t="n">
-        <v>0.7456140350877193</v>
+        <v>0.75</v>
       </c>
       <c r="M99" t="n">
-        <v>0.9340659340659341</v>
+        <v>0.9560439560439561</v>
       </c>
       <c r="N99" t="n">
-        <v>0.8292682926829267</v>
+        <v>0.8405797101449275</v>
       </c>
       <c r="O99" t="n">
         <v>72</v>
@@ -7214,10 +7214,10 @@
         <v>29</v>
       </c>
       <c r="Q99" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R99" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="100">
@@ -7239,43 +7239,43 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G100" t="n">
-        <v>0.828125</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H100" t="n">
-        <v>0.828125</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I100" t="n">
-        <v>0.8904109589041096</v>
+        <v>0.881578947368421</v>
       </c>
       <c r="J100" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="K100" t="n">
-        <v>0.7975460122699386</v>
+        <v>0.8072289156626506</v>
       </c>
       <c r="L100" t="n">
-        <v>0.7899159663865546</v>
+        <v>0.8017241379310345</v>
       </c>
       <c r="M100" t="n">
-        <v>0.9215686274509803</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="N100" t="n">
-        <v>0.8506787330316742</v>
+        <v>0.8532110091743118</v>
       </c>
       <c r="O100" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P100" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Q100" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R100" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="101">
@@ -7297,43 +7297,43 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G101" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.765625</v>
       </c>
       <c r="H101" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.765625</v>
       </c>
       <c r="I101" t="n">
-        <v>0.8295454545454546</v>
+        <v>0.7912087912087912</v>
       </c>
       <c r="J101" t="n">
-        <v>0.7448979591836735</v>
+        <v>0.7346938775510204</v>
       </c>
       <c r="K101" t="n">
-        <v>0.7849462365591399</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="L101" t="n">
-        <v>0.7596153846153846</v>
+        <v>0.7425742574257426</v>
       </c>
       <c r="M101" t="n">
-        <v>0.8404255319148937</v>
+        <v>0.7978723404255319</v>
       </c>
       <c r="N101" t="n">
-        <v>0.7979797979797979</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="O101" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P101" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q101" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="R101" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7327</v>
+        <v>7260</v>
       </c>
       <c r="C2" t="n">
-        <v>2227</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="3">
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1422</v>
+        <v>1417</v>
       </c>
       <c r="C3" t="n">
-        <v>8224</v>
+        <v>8229</v>
       </c>
     </row>
   </sheetData>
@@ -7436,16 +7436,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="C2" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E2" t="n">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3">
@@ -7455,16 +7455,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E3" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4">
@@ -7474,16 +7474,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="C4" t="n">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="D4" t="n">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E4" t="n">
-        <v>656</v>
+        <v>665</v>
       </c>
     </row>
     <row r="5">
@@ -7493,10 +7493,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>648</v>
+        <v>613</v>
       </c>
       <c r="C5" t="n">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="D5" t="n">
         <v>201</v>
@@ -7512,16 +7512,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C6" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D6" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E6" t="n">
-        <v>628</v>
+        <v>638</v>
       </c>
     </row>
     <row r="7">
@@ -7531,16 +7531,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="C7" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E7" t="n">
-        <v>811</v>
+        <v>813</v>
       </c>
     </row>
     <row r="8">
@@ -7550,16 +7550,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>711</v>
+        <v>699</v>
       </c>
       <c r="C8" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D8" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E8" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="9">
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>600</v>
+        <v>579</v>
       </c>
       <c r="C9" t="n">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="D9" t="n">
         <v>168</v>
@@ -7588,16 +7588,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C10" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D10" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E10" t="n">
-        <v>671</v>
+        <v>662</v>
       </c>
     </row>
     <row r="11">
@@ -7607,16 +7607,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C11" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D11" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E11" t="n">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="12">
@@ -7626,16 +7626,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E12" t="n">
-        <v>762</v>
+        <v>776</v>
       </c>
     </row>
     <row r="13">
@@ -7645,16 +7645,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C13" t="n">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="D13" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E13" t="n">
-        <v>610</v>
+        <v>605</v>
       </c>
     </row>
     <row r="14">
@@ -7664,16 +7664,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C14" t="n">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D14" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E14" t="n">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
   </sheetData>
